--- a/data/trans_dic/P1404-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1404-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 8,47</t>
+          <t>3,17; 8,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 14,18</t>
+          <t>6,45; 13,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 17,05</t>
+          <t>9,25; 17,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 16,5</t>
+          <t>9,6; 16,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 14,23</t>
+          <t>6,88; 14,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 16,92</t>
+          <t>8,9; 17,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,57; 17,98</t>
+          <t>9,83; 18,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,3; 18,91</t>
+          <t>11,49; 17,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 9,99</t>
+          <t>5,46; 9,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,49; 14,1</t>
+          <t>8,83; 14,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,41; 16,36</t>
+          <t>10,56; 16,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,59; 16,3</t>
+          <t>11,36; 16,07</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,56</t>
+          <t>5,24; 10,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,34; 16,97</t>
+          <t>10,31; 16,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 14,6</t>
+          <t>8,77; 14,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,55; 14,16</t>
+          <t>9,2; 15,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 12,99</t>
+          <t>7,74; 12,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 19,02</t>
+          <t>12,71; 19,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 17,88</t>
+          <t>11,05; 17,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,12; 16,02</t>
+          <t>10,96; 15,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 10,79</t>
+          <t>7,26; 10,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 16,94</t>
+          <t>12,26; 16,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,77; 15,14</t>
+          <t>10,81; 14,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,44; 14,17</t>
+          <t>10,55; 14,29</t>
         </is>
       </c>
     </row>
@@ -944,27 +944,27 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>14,83%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,39</t>
+          <t>5,46; 11,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 14,69</t>
+          <t>7,69; 14,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 16,93</t>
+          <t>9,71; 16,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,46; 18,54</t>
+          <t>11,73; 18,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 11,64</t>
+          <t>5,61; 11,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 17,27</t>
+          <t>10,06; 17,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,35; 19,17</t>
+          <t>10,97; 19,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 19,94</t>
+          <t>13,5; 19,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,52</t>
+          <t>6,14; 10,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 14,68</t>
+          <t>9,43; 14,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 16,47</t>
+          <t>11,23; 16,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,51; 18,22</t>
+          <t>13,51; 17,98</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 9,46</t>
+          <t>4,23; 9,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,31; 15,88</t>
+          <t>8,53; 15,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 16,46</t>
+          <t>9,49; 16,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 20,83</t>
+          <t>11,81; 20,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,47</t>
+          <t>4,05; 8,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,79; 19,71</t>
+          <t>12,65; 20,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 18,76</t>
+          <t>11,42; 18,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 17,67</t>
+          <t>13,35; 18,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,04</t>
+          <t>4,73; 8,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 16,59</t>
+          <t>11,66; 16,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 16,25</t>
+          <t>11,29; 16,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 17,42</t>
+          <t>13,7; 18,37</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,12; 16,53</t>
+          <t>7,49; 16,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,75; 22,06</t>
+          <t>11,72; 22,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 17,81</t>
+          <t>9,01; 17,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,75; 25,83</t>
+          <t>15,41; 23,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,59</t>
+          <t>6,54; 15,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,5; 28,49</t>
+          <t>16,67; 28,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,69; 19,92</t>
+          <t>10,26; 19,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,02; 29,82</t>
+          <t>21,39; 28,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 14,16</t>
+          <t>7,87; 14,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,96; 23,73</t>
+          <t>15,17; 23,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,89; 17,84</t>
+          <t>10,81; 17,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,41; 26,94</t>
+          <t>19,51; 25,05</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,79</t>
+          <t>3,24; 9,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,82; 18,47</t>
+          <t>9,93; 17,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,18; 14,51</t>
+          <t>7,35; 15,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,25; 25,05</t>
+          <t>16,64; 24,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,81; 17,48</t>
+          <t>9,68; 17,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,47; 20,02</t>
+          <t>11,36; 19,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,36; 14,95</t>
+          <t>7,41; 15,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,63; 21,22</t>
+          <t>14,76; 21,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,45</t>
+          <t>7,45; 12,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,96; 18,04</t>
+          <t>11,98; 18,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 13,49</t>
+          <t>8,07; 13,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,75; 21,95</t>
+          <t>16,71; 21,82</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,57</t>
+          <t>4,56; 8,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,67; 13,96</t>
+          <t>8,99; 14,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 13,83</t>
+          <t>8,56; 13,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,04; 18,94</t>
+          <t>13,77; 19,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,67; 13,97</t>
+          <t>8,55; 13,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,09; 14,65</t>
+          <t>9,09; 14,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,2; 13,21</t>
+          <t>8,25; 13,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,74; 74,41</t>
+          <t>16,2; 21,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,12; 10,39</t>
+          <t>7,19; 10,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,69; 13,32</t>
+          <t>9,57; 13,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,03; 12,59</t>
+          <t>9,16; 12,89</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,77; 58,56</t>
+          <t>15,8; 19,44</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,67; 13,12</t>
+          <t>8,62; 13,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,6; 11,17</t>
+          <t>6,4; 10,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,11; 12,45</t>
+          <t>8,22; 12,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,66; 11,87</t>
+          <t>9,09; 12,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,42</t>
+          <t>9,42; 14,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,09</t>
+          <t>9,36; 13,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,66</t>
+          <t>11,52; 16,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,11; 16,75</t>
+          <t>11,3; 15,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,75; 12,87</t>
+          <t>9,73; 12,94</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,69</t>
+          <t>8,56; 11,64</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,37; 13,92</t>
+          <t>10,43; 13,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,46; 13,27</t>
+          <t>10,88; 13,59</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,9</t>
+          <t>6,95; 8,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,2; 12,53</t>
+          <t>10,26; 12,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,41; 12,58</t>
+          <t>10,41; 12,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,6; 14,93</t>
+          <t>13,3; 15,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,25; 11,4</t>
+          <t>9,24; 11,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,61; 15,0</t>
+          <t>12,56; 14,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,1; 14,5</t>
+          <t>12,06; 14,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,67; 35,12</t>
+          <t>15,14; 17,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,44; 9,89</t>
+          <t>8,45; 9,83</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,79; 13,39</t>
+          <t>11,77; 13,4</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,19</t>
+          <t>11,48; 13,19</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,35; 27,09</t>
+          <t>14,56; 15,99</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39867</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43999</t>
+          <t>45881</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83866</t>
+          <t>86031</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8897; 23119</t>
+          <t>8658; 22770</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19128; 41802</t>
+          <t>19021; 41243</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26264; 50100</t>
+          <t>27175; 52262</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29827; 51374</t>
+          <t>30597; 52572</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17283; 37117</t>
+          <t>17941; 36952</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25262; 48598</t>
+          <t>25568; 49694</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27635; 51899</t>
+          <t>28387; 54377</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35618; 54781</t>
+          <t>36322; 55553</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29318; 53335</t>
+          <t>29139; 53160</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49437; 82088</t>
+          <t>51384; 82926</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60619; 95300</t>
+          <t>61482; 95453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>69683; 97978</t>
+          <t>72106; 102012</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>62592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>67774</t>
+          <t>71077</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>126215</t>
+          <t>133669</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27820; 52060</t>
+          <t>25820; 49787</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52144; 85570</t>
+          <t>51979; 85391</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43763; 73361</t>
+          <t>44097; 71512</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44167; 73140</t>
+          <t>48666; 82672</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38869; 65465</t>
+          <t>39026; 65487</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66249; 99614</t>
+          <t>66573; 100656</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59317; 93536</t>
+          <t>57780; 90689</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57055; 82226</t>
+          <t>59674; 84305</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72454; 107564</t>
+          <t>72379; 107690</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>125518; 174092</t>
+          <t>126009; 173422</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110449; 155286</t>
+          <t>110901; 153450</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>107473; 145857</t>
+          <t>113264; 153384</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46795</t>
+          <t>46247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>105111</t>
+          <t>105798</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17312; 36318</t>
+          <t>17411; 36209</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24906; 47586</t>
+          <t>24920; 46823</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30948; 53933</t>
+          <t>30939; 53121</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36141; 58499</t>
+          <t>36987; 58715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19217; 39028</t>
+          <t>18816; 38850</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32421; 58877</t>
+          <t>34318; 60365</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38166; 64478</t>
+          <t>36886; 64580</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47963; 69602</t>
+          <t>48107; 70434</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40593; 68804</t>
+          <t>40167; 67605</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65006; 97601</t>
+          <t>62700; 99484</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72566; 107871</t>
+          <t>73570; 108439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89805; 121128</t>
+          <t>90737; 120764</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50337</t>
+          <t>58078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62981</t>
+          <t>67594</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>113318</t>
+          <t>125672</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15543; 33930</t>
+          <t>15179; 33765</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31064; 59404</t>
+          <t>31883; 58661</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35088; 60878</t>
+          <t>35125; 60079</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38124; 65118</t>
+          <t>44085; 75380</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14582; 31450</t>
+          <t>15051; 32233</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49741; 76648</t>
+          <t>49204; 78682</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43760; 72655</t>
+          <t>44214; 72123</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39589; 84062</t>
+          <t>56347; 79979</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33811; 58677</t>
+          <t>34503; 60576</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>89252; 126558</t>
+          <t>88937; 127918</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83619; 123022</t>
+          <t>85507; 122859</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>81067; 137329</t>
+          <t>108959; 146058</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37178</t>
+          <t>39822</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>53389</t>
+          <t>56147</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90567</t>
+          <t>95969</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14483; 33612</t>
+          <t>15220; 33951</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24977; 46912</t>
+          <t>24917; 47516</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18322; 37623</t>
+          <t>19039; 37961</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29948; 46172</t>
+          <t>31686; 49298</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13988; 32373</t>
+          <t>13587; 31792</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36222; 62556</t>
+          <t>36614; 61857</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23365; 43540</t>
+          <t>22431; 42979</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45669; 61858</t>
+          <t>48333; 64712</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33124; 58197</t>
+          <t>32356; 58256</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68967; 102582</t>
+          <t>65545; 99579</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46796; 76677</t>
+          <t>46482; 74323</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>78811; 104021</t>
+          <t>84198; 108125</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56024</t>
+          <t>55001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>45307</t>
+          <t>46429</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>101331</t>
+          <t>101431</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9122; 23800</t>
+          <t>8772; 24434</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26906; 50606</t>
+          <t>27211; 49267</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18879; 38178</t>
+          <t>19328; 39462</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46517; 67530</t>
+          <t>45049; 67125</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27296; 48606</t>
+          <t>26929; 49627</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31901; 55686</t>
+          <t>31588; 55598</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20095; 40827</t>
+          <t>20241; 41236</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37512; 54397</t>
+          <t>38822; 55490</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41151; 68361</t>
+          <t>40898; 68015</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>66043; 99569</t>
+          <t>66115; 101961</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42179; 72355</t>
+          <t>43285; 72317</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>88122; 115456</t>
+          <t>89193; 116472</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98693</t>
+          <t>118694</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>323246</t>
+          <t>141583</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>421939</t>
+          <t>260277</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29220; 52720</t>
+          <t>28071; 52586</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>57478; 92542</t>
+          <t>59610; 95055</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56626; 90819</t>
+          <t>56173; 90380</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>80694; 117185</t>
+          <t>98223; 140359</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>55363; 89132</t>
+          <t>54538; 85885</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>63067; 101669</t>
+          <t>63037; 98266</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56688; 91311</t>
+          <t>57033; 93184</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>150158; 629880</t>
+          <t>124378; 162314</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>89280; 130200</t>
+          <t>90170; 129546</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131404; 180687</t>
+          <t>129893; 181394</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>121723; 169682</t>
+          <t>123521; 173750</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>245749; 858019</t>
+          <t>234107; 288019</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77316</t>
+          <t>86020</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>101305</t>
+          <t>111223</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>178621</t>
+          <t>197243</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>64512; 97595</t>
+          <t>64130; 99397</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>51440; 86997</t>
+          <t>49885; 84748</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>63157; 96934</t>
+          <t>64022; 98434</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33954; 110265</t>
+          <t>72538; 103275</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>75687; 112994</t>
+          <t>73846; 110024</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>77415; 115918</t>
+          <t>77015; 114594</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>95341; 137642</t>
+          <t>95164; 138209</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>86571; 119732</t>
+          <t>93757; 126422</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>148871; 196638</t>
+          <t>148564; 197567</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>136593; 187225</t>
+          <t>137040; 186432</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>166451; 223402</t>
+          <t>167433; 221752</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>106252; 218080</t>
+          <t>177167; 221178</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>464651</t>
+          <t>506606</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>756318</t>
+          <t>599485</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1220969</t>
+          <t>1106090</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>229997; 291763</t>
+          <t>227814; 290827</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>349516; 429276</t>
+          <t>351376; 433553</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>353501; 427026</t>
+          <t>353223; 424568</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>365988; 515380</t>
+          <t>468873; 550434</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>312640; 385338</t>
+          <t>312230; 383320</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>448403; 533428</t>
+          <t>446382; 532027</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>428803; 514035</t>
+          <t>427646; 514429</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>572572; 1282956</t>
+          <t>564001; 633319</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>561635; 658087</t>
+          <t>562402; 654366</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>822841; 934543</t>
+          <t>821373; 935342</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>802335; 915480</t>
+          <t>796559; 914997</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1019748; 1924356</t>
+          <t>1055483; 1159513</t>
         </is>
       </c>
     </row>
